--- a/data/trans_camb/P16A05-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P16A05-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 3,08</t>
+          <t>-1,5; 2,81</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 2,65</t>
+          <t>-1,3; 2,69</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,65; 6,8</t>
+          <t>1,32; 6,51</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,59; 4,92</t>
+          <t>0,63; 5,18</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,82; 7,34</t>
+          <t>1,88; 7,41</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,51; 13,0</t>
+          <t>7,16; 12,78</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,48; 3,62</t>
+          <t>0,35; 3,56</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,12; 4,66</t>
+          <t>1,17; 4,56</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,87; 9,84</t>
+          <t>5,74; 9,61</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-21,39; 87,51</t>
+          <t>-27,56; 79,11</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-26,13; 74,25</t>
+          <t>-24,38; 71,98</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>27,84; 180,81</t>
+          <t>21,63; 172,68</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,5; 71,15</t>
+          <t>6,68; 74,74</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>19,42; 102,81</t>
+          <t>21,04; 104,61</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>80,66; 180,57</t>
+          <t>76,37; 176,37</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,85; 61,01</t>
+          <t>4,88; 59,21</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>15,96; 80,24</t>
+          <t>15,87; 77,23</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>80,09; 169,83</t>
+          <t>79,46; 161,17</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,04; 1,97</t>
+          <t>0,14; 2,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,85; 2,71</t>
+          <t>0,75; 2,65</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,91; 3,3</t>
+          <t>0,98; 3,18</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,02; 2,78</t>
+          <t>-0,08; 2,84</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,25; 4,23</t>
+          <t>1,42; 4,18</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,27; 3,74</t>
+          <t>0,27; 3,66</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,31; 2,01</t>
+          <t>0,38; 2,12</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,38; 3,18</t>
+          <t>1,39; 3,13</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,14; 3,16</t>
+          <t>1,15; 3,22</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,01; 183,27</t>
+          <t>3,55; 197,22</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>43,41; 271,92</t>
+          <t>36,91; 256,7</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>46,61; 301,34</t>
+          <t>49,54; 285,8</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 90,27</t>
+          <t>-3,05; 89,56</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>27,18; 140,24</t>
+          <t>29,99; 138,42</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,12; 121,23</t>
+          <t>7,72; 122,9</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,87; 91,96</t>
+          <t>11,16; 98,38</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>44,18; 144,59</t>
+          <t>46,8; 149,36</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>38,73; 148,31</t>
+          <t>39,81; 144,38</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 3,63</t>
+          <t>-1,38; 3,36</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,79; 2,34</t>
+          <t>-1,69; 2,13</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,93; 1,68</t>
+          <t>-1,8; 1,62</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 3,34</t>
+          <t>-1,37; 3,12</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 1,89</t>
+          <t>-2,36; 1,61</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,64; 2,17</t>
+          <t>-1,6; 2,05</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 2,61</t>
+          <t>-0,6; 2,62</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 1,44</t>
+          <t>-1,46; 1,37</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 1,51</t>
+          <t>-1,01; 1,48</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-45,78; 230,83</t>
+          <t>-47,38; 210,63</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-52,39; 151,87</t>
+          <t>-52,79; 142,59</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-57,39; 119,37</t>
+          <t>-51,86; 106,94</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-39,82; 177,4</t>
+          <t>-40,26; 170,33</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-60,37; 100,99</t>
+          <t>-61,57; 116,01</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-38,7; 138,72</t>
+          <t>-39,93; 121,11</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-27,12; 127,66</t>
+          <t>-21,41; 133,38</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-44,98; 76,18</t>
+          <t>-42,36; 70,93</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-33,32; 82,32</t>
+          <t>-29,99; 80,03</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 1,67</t>
+          <t>-0,12; 1,71</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 1,7</t>
+          <t>0,1; 1,72</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,37; 2,51</t>
+          <t>0,49; 2,5</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,62; 2,89</t>
+          <t>0,68; 3,04</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,12; 3,49</t>
+          <t>1,14; 3,54</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,06; 3,86</t>
+          <t>1,14; 3,83</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,59; 2,06</t>
+          <t>0,56; 2,08</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,91; 2,39</t>
+          <t>0,89; 2,4</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,19; 2,95</t>
+          <t>1,12; 2,97</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-3,03; 76,02</t>
+          <t>-4,23; 77,24</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 78,59</t>
+          <t>3,3; 78,07</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>12,55; 107,87</t>
+          <t>17,02; 110,88</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9,97; 59,83</t>
+          <t>10,93; 63,98</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>17,91; 71,74</t>
+          <t>18,8; 74,0</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>19,07; 80,47</t>
+          <t>21,77; 79,08</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,47; 55,97</t>
+          <t>11,69; 55,86</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>20,21; 64,36</t>
+          <t>20,23; 65,18</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>29,08; 80,83</t>
+          <t>25,66; 79,36</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P16A05-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P16A05-Estudios-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3,92</t>
+          <t>3,76</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,86</t>
+          <t>9,39</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>7,57</t>
+          <t>7,16</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 2,81</t>
+          <t>-1,31; 2,87</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 2,69</t>
+          <t>-1,33; 2,89</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,32; 6,51</t>
+          <t>1,46; 6,24</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,63; 5,18</t>
+          <t>0,74; 5,1</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,88; 7,41</t>
+          <t>1,88; 7,16</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,16; 12,78</t>
+          <t>6,65; 11,78</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,35; 3,56</t>
+          <t>0,32; 3,54</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,17; 4,56</t>
+          <t>1,05; 4,52</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,74; 9,61</t>
+          <t>5,28; 8,96</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>86,53%</t>
+          <t>82,95%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>120,87%</t>
+          <t>115,03%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>115,34%</t>
+          <t>109,01%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-27,56; 79,11</t>
+          <t>-25,76; 75,37</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-24,38; 71,98</t>
+          <t>-25,72; 81,12</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>21,63; 172,68</t>
+          <t>24,36; 169,78</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,68; 74,74</t>
+          <t>7,2; 69,56</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>21,04; 104,61</t>
+          <t>20,73; 98,46</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>76,37; 176,37</t>
+          <t>70,68; 161,62</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,88; 59,21</t>
+          <t>4,23; 58,6</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>15,87; 77,23</t>
+          <t>14,19; 75,84</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>79,46; 161,17</t>
+          <t>71,36; 153,6</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2,17</t>
+          <t>2,45</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,22</t>
+          <t>2,96</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2,21</t>
+          <t>2,72</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,14; 2,0</t>
+          <t>0,15; 2,12</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,75; 2,65</t>
+          <t>0,79; 2,71</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,98; 3,18</t>
+          <t>1,52; 3,47</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,08; 2,84</t>
+          <t>-0,15; 2,77</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,42; 4,18</t>
+          <t>1,38; 4,33</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,27; 3,66</t>
+          <t>1,68; 4,33</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,38; 2,12</t>
+          <t>0,39; 2,02</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,39; 3,13</t>
+          <t>1,39; 3,14</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,15; 3,22</t>
+          <t>1,86; 3,43</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>151,11%</t>
+          <t>171,05%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>59,26%</t>
+          <t>79,19%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>86,81%</t>
+          <t>106,83%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,55; 197,22</t>
+          <t>2,25; 192,13</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>36,91; 256,7</t>
+          <t>39,18; 248,0</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>49,54; 285,8</t>
+          <t>77,24; 347,44</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-3,05; 89,56</t>
+          <t>-3,85; 83,15</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>29,99; 138,42</t>
+          <t>29,61; 143,11</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,72; 122,9</t>
+          <t>35,64; 147,38</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>11,16; 98,38</t>
+          <t>11,01; 90,3</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>46,8; 149,36</t>
+          <t>46,92; 146,97</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>39,81; 144,38</t>
+          <t>62,26; 154,1</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>-0,21</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,46</t>
+          <t>0,47</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,25</t>
+          <t>0,15</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 3,36</t>
+          <t>-1,44; 3,37</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,69; 2,13</t>
+          <t>-1,54; 2,12</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 1,62</t>
+          <t>-1,96; 1,33</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 3,12</t>
+          <t>-1,58; 3,31</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,36; 1,61</t>
+          <t>-2,33; 1,96</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 2,05</t>
+          <t>-1,47; 2,17</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 2,62</t>
+          <t>-0,77; 2,46</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,46; 1,37</t>
+          <t>-1,45; 1,42</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 1,48</t>
+          <t>-1,27; 1,32</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>-8,67%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>16,73%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>5,73%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-47,38; 210,63</t>
+          <t>-47,41; 217,51</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-52,79; 142,59</t>
+          <t>-49,88; 146,41</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-51,86; 106,94</t>
+          <t>-55,93; 90,71</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-40,26; 170,33</t>
+          <t>-42,83; 196,18</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-61,57; 116,01</t>
+          <t>-62,18; 119,57</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-39,93; 121,11</t>
+          <t>-38,11; 124,4</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-21,41; 133,38</t>
+          <t>-24,91; 123,94</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-42,36; 70,93</t>
+          <t>-43,5; 75,99</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-29,99; 80,03</t>
+          <t>-37,18; 72,16</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1,53</t>
+          <t>1,69</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,63</t>
+          <t>3,08</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2,11</t>
+          <t>2,43</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,12; 1,71</t>
+          <t>-0,13; 1,58</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,1; 1,72</t>
+          <t>0,02; 1,74</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,49; 2,5</t>
+          <t>0,85; 2,63</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,68; 3,04</t>
+          <t>0,58; 2,92</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,14; 3,54</t>
+          <t>1,13; 3,53</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,14; 3,83</t>
+          <t>2,02; 4,14</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,56; 2,08</t>
+          <t>0,6; 2,12</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,89; 2,4</t>
+          <t>0,85; 2,3</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,12; 2,97</t>
+          <t>1,72; 3,14</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>59,11%</t>
+          <t>65,61%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>49,25%</t>
+          <t>57,85%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>53,0%</t>
+          <t>60,99%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-4,23; 77,24</t>
+          <t>-6,2; 70,66</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3,3; 78,07</t>
+          <t>0,73; 77,15</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>17,02; 110,88</t>
+          <t>27,81; 119,41</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10,93; 63,98</t>
+          <t>9,5; 59,28</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>18,8; 74,0</t>
+          <t>17,43; 71,1</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>21,77; 79,08</t>
+          <t>33,56; 88,45</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>11,69; 55,86</t>
+          <t>13,22; 56,2</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>20,23; 65,18</t>
+          <t>19,29; 63,06</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>25,66; 79,36</t>
+          <t>39,78; 87,86</t>
         </is>
       </c>
     </row>
